--- a/docs/documents/zone-5b-classified.xlsx
+++ b/docs/documents/zone-5b-classified.xlsx
@@ -59,6 +59,10 @@
     <col min="4" max="4" width="37" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="53" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -92,6 +96,26 @@
           <t>rationale</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>topic_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t>mixed_flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -124,6 +148,26 @@
           <t>explicitly disagrees with changes</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -156,6 +200,26 @@
           <t>conditional on more parking</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Parking; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -188,6 +252,26 @@
           <t>asks about building impacts</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -220,6 +304,26 @@
           <t>opposes changes over parking</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -252,6 +356,26 @@
           <t>opposes new development</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -284,6 +408,26 @@
           <t>not in favor</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -316,6 +460,26 @@
           <t>rejects parking reduction and density</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parking; Density</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -348,6 +512,26 @@
           <t>supports more housing and business</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -380,6 +564,26 @@
           <t>approves proposal</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -412,6 +616,26 @@
           <t>agrees with proposal</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -444,6 +668,26 @@
           <t>opposes taller buildings</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -476,6 +720,26 @@
           <t>rejects high rises</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -508,6 +772,26 @@
           <t>wants park preserved</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -540,6 +824,26 @@
           <t>supports with affordability caveat</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Affordable housing</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -572,6 +876,26 @@
           <t>explicitly rejects proposal</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -604,6 +928,26 @@
           <t>supports higher building here</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -636,6 +980,26 @@
           <t>warns against added density</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -668,6 +1032,26 @@
           <t>questions apartments and parking</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Parking; Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -700,6 +1084,26 @@
           <t>rejects more building and density</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -732,6 +1136,26 @@
           <t>explicitly opposes zoning changes</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -764,6 +1188,26 @@
           <t>rejects limited parking provisions</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -796,6 +1240,26 @@
           <t>opposes apartments and added people</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -828,6 +1292,26 @@
           <t>not sure</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -860,6 +1344,26 @@
           <t>says fine there</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -892,6 +1396,26 @@
           <t>concerned about congestion</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -924,6 +1448,26 @@
           <t>views proposal as harmful</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -956,6 +1500,26 @@
           <t>supports with sidewalk caveat</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -988,6 +1552,26 @@
           <t>not supportive</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1020,6 +1604,26 @@
           <t>no clear stance on Montgomery</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1052,6 +1656,26 @@
           <t>calls it terrible with parking harm</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1084,6 +1708,26 @@
           <t>disagrees with all changes</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1116,6 +1760,26 @@
           <t>asks for negatives</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1148,6 +1812,26 @@
           <t>hostile to proposal</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1180,6 +1864,26 @@
           <t>wants park without development</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1212,6 +1916,26 @@
           <t>against due parking pressure</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1244,6 +1968,26 @@
           <t>rejects height and parking changes</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1276,6 +2020,26 @@
           <t>somewhat okay with reservations</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1308,6 +2072,26 @@
           <t>opposes reduced parking</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1340,6 +2124,26 @@
           <t>fine with plan</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1372,6 +2176,26 @@
           <t>rejects reduced parking</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1404,6 +2228,26 @@
           <t>supports height and less parking</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1436,6 +2280,26 @@
           <t>loves it</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1468,6 +2332,26 @@
           <t>positive response</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1500,6 +2384,26 @@
           <t>calls idea terrible</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1532,6 +2436,26 @@
           <t>strongly against</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1564,6 +2488,26 @@
           <t>criticizes drafters</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1596,6 +2540,26 @@
           <t>limits floors below proposal</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1628,6 +2592,26 @@
           <t>rejects density height and parking</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Parking; Building height; Density</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1660,6 +2644,26 @@
           <t>rejects high rise</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1692,6 +2696,26 @@
           <t>dislikes revenue driven change</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1724,6 +2748,26 @@
           <t>calls proposal terrible</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1756,6 +2800,26 @@
           <t>rejects parking and height bonus</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Parking; Building height; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1788,6 +2852,26 @@
           <t>rejects additional stories</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1820,6 +2904,26 @@
           <t>disapproves all zoning changes</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1852,6 +2956,26 @@
           <t>says no good</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1884,6 +3008,26 @@
           <t>rejects parking reduction and height</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1916,6 +3060,26 @@
           <t>against it</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1948,6 +3112,26 @@
           <t>says ignores resident wishes</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1980,6 +3164,26 @@
           <t>prefers no growth due traffic</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2012,6 +3216,26 @@
           <t>says destroying Narberth</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2044,6 +3268,26 @@
           <t>rejects height increase</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2076,6 +3320,26 @@
           <t>opposes stories and parking change</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2108,6 +3372,26 @@
           <t>frames as developer driven</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Developer incentives</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2140,6 +3424,26 @@
           <t>supports reduced parking</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2172,6 +3476,26 @@
           <t>asks rejection</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2204,6 +3528,26 @@
           <t>supports changes with caveats</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2236,6 +3580,26 @@
           <t>no substantive stance</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2268,6 +3632,26 @@
           <t>opposes reduced parking</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2300,6 +3684,26 @@
           <t>says reasonable</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2332,6 +3736,26 @@
           <t>rejects reduced parking</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2364,6 +3788,26 @@
           <t>supports less parking</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2396,6 +3840,26 @@
           <t>rejects parking limits</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2428,6 +3892,26 @@
           <t>rejects height increase</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2460,6 +3944,26 @@
           <t>supports lower parking minimums</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2492,6 +3996,26 @@
           <t>opposes more growth</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2524,6 +4048,26 @@
           <t>opposes parking reductions</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2556,6 +4100,26 @@
           <t>cites density congestion parking</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Parking; Traffic and safety; Density</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2588,6 +4152,26 @@
           <t>supports only smaller buildings</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2620,6 +4204,26 @@
           <t>says fine</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2652,6 +4256,26 @@
           <t>opposed</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2684,6 +4308,26 @@
           <t>strongly against</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2716,6 +4360,26 @@
           <t>rejects five stories and parking reduction</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2748,6 +4412,26 @@
           <t>says not needed</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2780,6 +4464,26 @@
           <t>alleges developer corruption</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Developer incentives</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2812,6 +4516,26 @@
           <t>says no</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2844,6 +4568,26 @@
           <t>seems okay with caveat</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2876,6 +4620,26 @@
           <t>fine with this</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2908,6 +4672,26 @@
           <t>not good</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2940,6 +4724,26 @@
           <t>not applicable</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2972,6 +4776,26 @@
           <t>opposes height bonus and reduced parking</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Parking; Building height; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3004,6 +4828,26 @@
           <t>Supports these changes</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3036,6 +4880,26 @@
           <t>rejects more business activity</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3068,6 +4932,26 @@
           <t>opposes reduced parking</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3100,6 +4984,26 @@
           <t>agrees</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3132,6 +5036,26 @@
           <t>does not support proposal</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3164,6 +5088,26 @@
           <t>rejects four and five story buildings</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3196,6 +5140,26 @@
           <t>opposes mid rise buildings</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3228,6 +5192,26 @@
           <t>disagrees</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3260,6 +5244,26 @@
           <t>rejects four stories and parking</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3292,6 +5296,26 @@
           <t>seems okay</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3324,6 +5348,26 @@
           <t>rejects more people</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3356,6 +5400,26 @@
           <t>says it makes sense</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3388,6 +5452,26 @@
           <t>opposes apartment construction</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3420,6 +5504,26 @@
           <t>cites traffic nightmare</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3452,6 +5556,26 @@
           <t>against density anywhere</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3484,6 +5608,26 @@
           <t>dislikes parking assumptions</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3516,6 +5660,26 @@
           <t>opposes more apartments</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3548,6 +5712,26 @@
           <t>does not support multifamily</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3580,6 +5764,26 @@
           <t>warns not to overwhelm area</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3612,6 +5816,26 @@
           <t>opposes tall buildings</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3644,6 +5868,26 @@
           <t>opposes upzoning and parking</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3676,6 +5920,26 @@
           <t>very opposed</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3708,6 +5972,26 @@
           <t>strongly disagree</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3740,6 +6024,26 @@
           <t>prefers visitors over residents</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3772,6 +6076,26 @@
           <t>criticizes increasing density</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3804,6 +6128,26 @@
           <t>says do not develop</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3836,6 +6180,26 @@
           <t>opposes too tall buildings</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3868,6 +6232,26 @@
           <t>wants delay until traffic calming</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3900,6 +6284,26 @@
           <t>not opposed to changes</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3932,6 +6336,26 @@
           <t>supports growth and changes</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3964,6 +6388,26 @@
           <t>opposes due to parking</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3996,6 +6440,26 @@
           <t>seems fine</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4028,6 +6492,26 @@
           <t>agrees with zoning changes</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4060,6 +6544,26 @@
           <t>agrees with them</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4092,6 +6596,26 @@
           <t>wants affordable housing</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Affordable housing</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4124,6 +6648,26 @@
           <t>calls plan reasonable</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4156,6 +6700,26 @@
           <t>wants more parking lots</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4188,6 +6752,26 @@
           <t>does not like it</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4220,6 +6804,26 @@
           <t>explicitly in favor</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4252,6 +6856,26 @@
           <t>worries about traffic impact</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4284,6 +6908,26 @@
           <t>in agreement</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4316,6 +6960,26 @@
           <t>height is ok</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4348,6 +7012,26 @@
           <t>opposes height and units</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Building height; Density</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4380,6 +7064,26 @@
           <t>higher heights are ok</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4412,6 +7116,26 @@
           <t>opposes parking reduction and affordability</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Parking; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4444,6 +7168,26 @@
           <t>needs more info</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4476,6 +7220,26 @@
           <t>accepts Montgomery changes</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4508,6 +7272,26 @@
           <t>too dense and too little parking</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Parking; Density</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4540,6 +7324,26 @@
           <t>no more apartments</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4572,6 +7376,26 @@
           <t>opposes more housing</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4604,6 +7428,26 @@
           <t>unsure</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4636,6 +7480,26 @@
           <t>against height density parking reduction</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Parking; Building height; Density</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4668,6 +7532,26 @@
           <t>opposes parking reduction</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4700,6 +7584,26 @@
           <t>needs more parking</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4732,6 +7636,26 @@
           <t>opposes height and parking variances</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4764,6 +7688,26 @@
           <t>agrees with it</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4796,6 +7740,26 @@
           <t>opposes apartments</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4828,6 +7792,26 @@
           <t>cites parking and safety</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Parking; Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4860,6 +7844,26 @@
           <t>opposes parking reduction</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4892,6 +7896,26 @@
           <t>unclear commercial comment</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4924,6 +7948,26 @@
           <t>opposes dense development</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4956,6 +8000,26 @@
           <t>mixed affordability concern</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Affordable housing; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4988,6 +8052,26 @@
           <t>opposes less parking</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5020,6 +8104,26 @@
           <t>disagrees</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5052,6 +8156,26 @@
           <t>ok with it despite question</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5084,6 +8208,26 @@
           <t>does not approve</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5116,6 +8260,26 @@
           <t>concerned about apartment parking</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Parking; Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5148,6 +8312,26 @@
           <t>opposes five story buildings</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5180,6 +8364,26 @@
           <t>opposes parking ratio</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5212,6 +8416,26 @@
           <t>does not agree</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5244,6 +8468,26 @@
           <t>good in general</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5276,6 +8520,26 @@
           <t>opposes reduced parking</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5308,6 +8572,26 @@
           <t>opposes height and parking change</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5340,6 +8624,26 @@
           <t>ok with zoning changes</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5372,6 +8676,26 @@
           <t>does not approve</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5404,6 +8728,26 @@
           <t>parking would be problem</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5436,6 +8780,26 @@
           <t>against the plans</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5468,6 +8832,26 @@
           <t>opposes high rises</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5500,6 +8884,26 @@
           <t>opposes height and parking reduction</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5532,6 +8936,26 @@
           <t>sounds good</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5564,6 +8988,26 @@
           <t>should not continue as described</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5596,6 +9040,26 @@
           <t>likes this idea</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5628,6 +9092,26 @@
           <t>good with parking concern</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5660,6 +9144,26 @@
           <t>warns overcrowding</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5692,6 +9196,26 @@
           <t>opposes additional housing</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5724,6 +9248,26 @@
           <t>reference unclear</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5756,6 +9300,26 @@
           <t>implies loss of character</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Neighborhood character</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5788,6 +9352,26 @@
           <t>more the better</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5820,6 +9404,26 @@
           <t>support</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5852,6 +9456,26 @@
           <t>opposes attracting lower income residents</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5884,6 +9508,26 @@
           <t>supports height and mixed use</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Building height; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5916,6 +9560,26 @@
           <t>positive response</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5948,6 +9612,26 @@
           <t>completely oppose it</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5980,6 +9664,26 @@
           <t>opposes eased parking</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6012,6 +9716,26 @@
           <t>wants stronger density incentive</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Density; Developer incentives</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6044,6 +9768,26 @@
           <t>opposes adding traffic and parking</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Parking; Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6076,6 +9820,26 @@
           <t>calls changes positive</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6108,6 +9872,26 @@
           <t>calls changes misuse of power</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6140,6 +9924,26 @@
           <t>encourages business growth</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6172,6 +9976,26 @@
           <t>emphatic no</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6204,6 +10028,26 @@
           <t>blank response</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6236,6 +10080,26 @@
           <t>no way</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6268,6 +10132,26 @@
           <t>opposes five story buildings</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6300,6 +10184,26 @@
           <t>opposes tall buildings</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6332,6 +10236,26 @@
           <t>supports proposed changes</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6364,6 +10288,26 @@
           <t>supports density bonus and parking reduction</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Parking; Density; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6396,6 +10340,26 @@
           <t>wants more affordable units</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Density; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6428,6 +10392,26 @@
           <t>opposes diminished parking</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6460,6 +10444,26 @@
           <t>calls plan poor</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6492,6 +10496,26 @@
           <t>seems okay</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6524,6 +10548,26 @@
           <t>opposes less parking</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6556,6 +10600,26 @@
           <t>too tall</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6588,6 +10652,26 @@
           <t>opposes overbuilding and minimal parking</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6620,6 +10704,26 @@
           <t>loves proactive change</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6652,6 +10756,26 @@
           <t>Non substantive response</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6684,6 +10808,26 @@
           <t>Opposes parking reduction and affordability</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Parking; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6716,6 +10860,26 @@
           <t>Rejects reduced parking and more residents</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6748,6 +10912,26 @@
           <t>Supports greater height and parking recommendations</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6780,6 +10964,26 @@
           <t>Agrees with proposal</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6812,6 +11016,26 @@
           <t>Cannot read materials</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6844,6 +11068,26 @@
           <t>Says no need for five stories</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6876,6 +11120,26 @@
           <t>Could accept five stories with affordability</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Building height; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6908,6 +11172,26 @@
           <t>Calls proposal poor and rejects parking reduction</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6940,6 +11224,26 @@
           <t>Calls changes a disaster</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6972,6 +11276,26 @@
           <t>Vehemently opposed to affordable housing</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Affordable housing</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7004,6 +11328,26 @@
           <t>Says zoning changes worsen problems</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7036,6 +11380,26 @@
           <t>Criticizes transit oriented development approach</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7068,6 +11432,26 @@
           <t>Opposes five story structure and traffic</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Traffic and safety; Building height</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7100,6 +11484,26 @@
           <t>Opposes fifth floor density bonus</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Density; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7132,6 +11536,26 @@
           <t>Rejects lowering development costs</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7164,6 +11588,26 @@
           <t>Questions added stories without representation</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7196,6 +11640,26 @@
           <t>Rejects five stories and reduced parking</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7228,6 +11692,26 @@
           <t>Says do not reduce parking</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7260,6 +11744,26 @@
           <t>Rejects YIMBY approach</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7292,6 +11796,26 @@
           <t>Negative credibility comment</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7324,6 +11848,26 @@
           <t>Says proposal makes sense</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7356,6 +11900,26 @@
           <t>Says traffic makes area unappealing</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Traffic and safety</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7388,6 +11952,26 @@
           <t>Rejects reduced parking</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7420,6 +12004,26 @@
           <t>Rejects fifth story and parking reduction</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Parking; Building height</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7452,6 +12056,26 @@
           <t>Supports upzoning and parking reform</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7484,6 +12108,26 @@
           <t>Rejects density push and parking allowances</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Parking; Density</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7516,6 +12160,26 @@
           <t>Supports walkable future with traffic calming</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Traffic and safety; Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7548,6 +12212,26 @@
           <t>Says it looks good</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7580,6 +12264,26 @@
           <t>Opposes further development</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7612,6 +12316,26 @@
           <t>Says density is out of character</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Density; Neighborhood character</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7644,6 +12368,26 @@
           <t>Requires at least one parking space</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7676,6 +12420,26 @@
           <t>Says parking is a non starter</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7708,6 +12472,26 @@
           <t>Says it makes sense</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7740,6 +12524,26 @@
           <t>Fine with changes with height caveat</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7772,6 +12576,26 @@
           <t>Rejects lower costs and parking reduction</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7804,6 +12628,26 @@
           <t>Votes no on density and developer benefits</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Density; Developer incentives</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7836,6 +12680,26 @@
           <t>Calls it a bad idea</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7868,6 +12732,26 @@
           <t>Wants original code kept</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7900,6 +12784,26 @@
           <t>Strongly not in favor of density</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7932,6 +12836,26 @@
           <t>Rejects five stories and low income housing</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7964,6 +12888,26 @@
           <t>Calls recommendations common sense</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7996,6 +12940,26 @@
           <t>Calls proposal ridiculous</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8028,6 +12992,26 @@
           <t>Says leave it alone</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8060,6 +13044,26 @@
           <t>Against five story buildings</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8092,6 +13096,26 @@
           <t>Absolutely against proposal</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8124,6 +13148,26 @@
           <t>Rejects reduced parking ratio</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8156,6 +13200,26 @@
           <t>Calls recommendations ridiculous</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8188,6 +13252,26 @@
           <t>Rejects height increase</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8220,6 +13304,26 @@
           <t>Rejects density bonus and parking reduction</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Parking; Density; Affordable housing</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8252,6 +13356,26 @@
           <t>Says yes</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8284,6 +13408,26 @@
           <t>Likes the changes</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8316,6 +13460,26 @@
           <t>Wants three stories or fewer</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8348,6 +13512,26 @@
           <t>Supports these changes</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8380,6 +13564,26 @@
           <t>Strongly against proposal</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8412,6 +13616,26 @@
           <t>Not in favor</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8444,6 +13668,26 @@
           <t>Objects to affordable housing narrative</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Affordable housing</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8476,6 +13720,26 @@
           <t>Supports dense apartments along Montgomery</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8508,6 +13772,26 @@
           <t>Says harmful to character</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Neighborhood character</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8540,6 +13824,26 @@
           <t>Says nobody wants it</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8572,6 +13876,26 @@
           <t>Opposes proposed apartments</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8604,6 +13928,26 @@
           <t>Fine with Montgomery development</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8636,6 +13980,26 @@
           <t>Rejects four story buildings</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8668,6 +14032,26 @@
           <t>Says it is acceptable</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8700,6 +14084,26 @@
           <t>Calls proposal nonsense</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8732,6 +14136,26 @@
           <t>Blank response</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8764,6 +14188,26 @@
           <t>Rejects parking reduction</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8796,6 +14240,26 @@
           <t>Says changes harm livability</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8828,6 +14292,26 @@
           <t>Rejects reducing parking below one</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8860,6 +14344,26 @@
           <t>Supports repurposing areas</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8892,6 +14396,26 @@
           <t>Calls it a great idea</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8924,6 +14448,26 @@
           <t>Negative overall reaction</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8956,6 +14500,26 @@
           <t>Concerned about home values</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Property values</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8988,6 +14552,26 @@
           <t>Vehemently opposes multipurpose buildings</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9020,6 +14604,26 @@
           <t>Says very good</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9052,6 +14656,26 @@
           <t>Raises parking problem and empty buildings</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9084,6 +14708,26 @@
           <t>Does not support changes</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9116,6 +14760,26 @@
           <t>Loves plan as progress</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9148,6 +14812,26 @@
           <t>Rejects affordable housing recommendation</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Affordable housing</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9180,6 +14864,26 @@
           <t>Opposes development without more parking</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9212,6 +14916,26 @@
           <t>Calls parking reduction insane</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9244,6 +14968,26 @@
           <t>Strongly opposes zoning changes</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>General opposition</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9276,6 +15020,26 @@
           <t>Says makes sense with environmental caveat</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9308,6 +15072,26 @@
           <t>Requires one parking space per unit</t>
         </is>
       </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9340,6 +15124,26 @@
           <t>States housing preference only</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Unclear or neutral</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9372,6 +15176,26 @@
           <t>Says stop building apartments</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Density; Conditional or mixed response</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9404,6 +15228,26 @@
           <t>Opposes if reduced parking is included</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9436,6 +15280,26 @@
           <t>Supports density and accessibility</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9468,6 +15332,26 @@
           <t>Would not support added stories</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9500,6 +15384,26 @@
           <t>Rejects parking requirement reduction</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9532,6 +15436,26 @@
           <t>Concerned about height and traffic</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Traffic and safety; Building height</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9564,6 +15488,26 @@
           <t>Encourages development there</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9596,6 +15540,26 @@
           <t>Says no taller buildings needed</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Building height</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9628,6 +15592,26 @@
           <t>Questions need for expansion</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>General stance</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9660,6 +15644,26 @@
           <t>Supports denser development</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9692,6 +15696,26 @@
           <t>One hundred percent support</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -9724,6 +15748,26 @@
           <t>Supports densification</t>
         </is>
       </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -9756,6 +15800,26 @@
           <t>Supports upzoning for housing and businesses</t>
         </is>
       </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Transit and walkability</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9788,8 +15852,28 @@
           <t>Strongly supports</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>General support</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F304"/>
+  <autoFilter ref="A1:J304"/>
 </worksheet>
 </file>
--- a/docs/documents/zone-5b-classified.xlsx
+++ b/docs/documents/zone-5b-classified.xlsx
@@ -410,7 +410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General support</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>General stance</t>
+          <t>General opposition</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
